--- a/5-png-inserter/out/test_fixture.xlsx
+++ b/5-png-inserter/out/test_fixture.xlsx
@@ -233,7 +233,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="4762500"/>
@@ -429,7 +429,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>305</row>
+      <row>325</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="5143500"/>
@@ -515,7 +515,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="8572500"/>
@@ -543,7 +543,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="1781175"/>
@@ -571,7 +571,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>164</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3257550"/>
@@ -599,7 +599,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>164</row>
+      <row>218</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3257550"/>
@@ -627,7 +627,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>218</row>
+      <row>272</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3257550"/>
@@ -655,7 +655,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>272</row>
+      <row>326</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="1609725"/>
@@ -683,7 +683,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>283</row>
+      <row>337</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3810000"/>
@@ -711,7 +711,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>306</row>
+      <row>360</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="1038225"/>
@@ -739,7 +739,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>314</row>
+      <row>379</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2143125"/>
@@ -1182,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K271"/>
+  <dimension ref="A1:K325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,29 +1255,29 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>BKK02</t>
-        </is>
-      </c>
-    </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>BKK03</t>
+          <t>BKK02</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>BKK04</t>
+          <t>BKK03</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>BKK04</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
         <is>
           <t>BKK09</t>
         </is>
@@ -1287,17 +1287,17 @@
   <mergeCells count="5">
     <mergeCell ref="A163:K163"/>
     <mergeCell ref="A271:K271"/>
-    <mergeCell ref="A109:K109"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A217:K217"/>
+    <mergeCell ref="A325:K325"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="109" min="0" max="16383" man="1"/>
     <brk id="163" min="0" max="16383" man="1"/>
     <brk id="217" min="0" max="16383" man="1"/>
     <brk id="271" min="0" max="16383" man="1"/>
+    <brk id="325" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/5-png-inserter/out/test_fixture.xlsx
+++ b/5-png-inserter/out/test_fixture.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.2 Alarm After" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2.1. Bayface_Before'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2.2. Bayface_After'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2.1. Bayface_Before'!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2.2. Bayface_After'!$1:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -233,7 +233,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="4762500"/>
@@ -261,7 +261,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2143125"/>
@@ -289,7 +289,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>164</row>
+      <row>140</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2143125"/>
@@ -317,7 +317,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>218</row>
+      <row>183</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2143125"/>
@@ -345,7 +345,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>272</row>
+      <row>226</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="685800"/>
@@ -373,7 +373,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>278</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2038350"/>
@@ -401,7 +401,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>291</row>
+      <row>245</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2219325"/>
@@ -429,7 +429,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>325</row>
+      <row>268</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="5143500"/>
@@ -515,7 +515,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="8572500"/>
@@ -543,7 +543,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="1781175"/>
@@ -571,7 +571,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>164</row>
+      <row>140</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3257550"/>
@@ -599,7 +599,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>218</row>
+      <row>183</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3257550"/>
@@ -627,7 +627,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>272</row>
+      <row>226</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3257550"/>
@@ -655,7 +655,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>326</row>
+      <row>269</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="1609725"/>
@@ -683,7 +683,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>337</row>
+      <row>280</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="3810000"/>
@@ -711,7 +711,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>360</row>
+      <row>303</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="1038225"/>
@@ -739,7 +739,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>379</row>
+      <row>311</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2857500" cy="2143125"/>
@@ -1053,9 +1053,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr autoPageBreaks="1"/>
   </sheetPr>
-  <dimension ref="A1:K271"/>
+  <dimension ref="A1:K225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,29 +1128,29 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>BKK02</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
         <is>
           <t>BKK03</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="1" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t>BKK04</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="1" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
         <is>
           <t>BKK09</t>
         </is>
@@ -1158,20 +1158,14 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A163:K163"/>
-    <mergeCell ref="A271:K271"/>
-    <mergeCell ref="A109:K109"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A96:K96"/>
+    <mergeCell ref="A182:K182"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A217:K217"/>
+    <mergeCell ref="A225:K225"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="4" manualBreakCount="4">
-    <brk id="109" min="0" max="16383" man="1"/>
-    <brk id="163" min="0" max="16383" man="1"/>
-    <brk id="217" min="0" max="16383" man="1"/>
-    <brk id="271" min="0" max="16383" man="1"/>
-  </rowBreaks>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1180,9 +1174,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr autoPageBreaks="1"/>
   </sheetPr>
-  <dimension ref="A1:K325"/>
+  <dimension ref="A1:K268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,29 +1249,29 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
         <is>
           <t>BKK02</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="1" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t>BKK03</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="1" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
         <is>
           <t>BKK04</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" s="1" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
         <is>
           <t>BKK09</t>
         </is>
@@ -1285,20 +1279,14 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A163:K163"/>
-    <mergeCell ref="A271:K271"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A182:K182"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A217:K217"/>
-    <mergeCell ref="A325:K325"/>
+    <mergeCell ref="A268:K268"/>
+    <mergeCell ref="A225:K225"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="4" manualBreakCount="4">
-    <brk id="163" min="0" max="16383" man="1"/>
-    <brk id="217" min="0" max="16383" man="1"/>
-    <brk id="271" min="0" max="16383" man="1"/>
-    <brk id="325" min="0" max="16383" man="1"/>
-  </rowBreaks>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
